--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41799-2025 artfynd.xlsx
+++ b/artfynd/A 41799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128497403</v>
       </c>
       <c r="B2" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
